--- a/data/excel/asset_state_events.xlsx
+++ b/data/excel/asset_state_events.xlsx
@@ -35,6 +35,33 @@
   </x:si>
   <x:si>
     <x:t>UsuarioId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>387ef049-8de7-4297-adcc-2efbcba6e701</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRUEBA-2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unavailable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T16:02:20.4196626Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test de cambios</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1dc348ae-ab97-4182-a1e4-b29d684dde2a</x:t>
+  </x:si>
+  <x:si>
+    <x:t>b6e3071e-3db6-4e1c-a702-9b6b16a449b4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-07-08T16:03:02.8459066Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test 2</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -400,16 +427,16 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G1"/>
+  <x:dimension ref="A1:G3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="8.996339" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="37.996339" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="12.853482" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="14.424911" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12.567768" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="7.567768" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="9.567768" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.139196" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="28.282054" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14.996339" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="37.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7">
@@ -433,6 +460,52 @@
       </x:c>
       <x:c r="G1" s="1" t="s">
         <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:7">
+      <x:c r="A2" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:7">
+      <x:c r="A3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
